--- a/diseases/d043/2000-2004.xlsx
+++ b/diseases/d043/2000-2004.xlsx
@@ -13072,11 +13072,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13089,7 +13084,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
@@ -13099,15 +13094,15 @@
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -13323,7 +13318,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
@@ -13333,15 +13328,15 @@
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -19430,11 +19425,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19447,7 +19437,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
@@ -19457,15 +19447,15 @@
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -19681,7 +19671,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
@@ -19691,15 +19681,15 @@
       </c>
       <c r="AS111" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -25783,11 +25773,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25800,7 +25785,7 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ143" t="inlineStr">
@@ -25810,15 +25795,15 @@
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
@@ -26034,7 +26019,7 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ144" t="inlineStr">
@@ -26044,15 +26029,15 @@
       </c>
       <c r="AS144" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
@@ -34076,11 +34061,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34093,7 +34073,7 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ186" t="inlineStr">
@@ -34103,15 +34083,15 @@
       </c>
       <c r="AS186" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
@@ -34327,7 +34307,7 @@
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ187" t="inlineStr">
@@ -34337,15 +34317,15 @@
       </c>
       <c r="AS187" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
@@ -40044,11 +40024,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA217" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40061,7 +40036,7 @@
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
@@ -40071,15 +40046,15 @@
       </c>
       <c r="AS217" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
@@ -40295,7 +40270,7 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ218" t="inlineStr">
@@ -40305,15 +40280,15 @@
       </c>
       <c r="AS218" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
@@ -46397,11 +46372,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46414,7 +46384,7 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ250" t="inlineStr">
@@ -46424,15 +46394,15 @@
       </c>
       <c r="AS250" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
@@ -46648,7 +46618,7 @@
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ251" t="inlineStr">
@@ -46658,15 +46628,15 @@
       </c>
       <c r="AS251" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
@@ -53530,11 +53500,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA287" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -53547,7 +53512,7 @@
       </c>
       <c r="AP287" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ287" t="inlineStr">
@@ -53557,15 +53522,15 @@
       </c>
       <c r="AS287" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV287" t="inlineStr">
@@ -53781,7 +53746,7 @@
       </c>
       <c r="AP288" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ288" t="inlineStr">
@@ -53791,15 +53756,15 @@
       </c>
       <c r="AS288" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT288" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV288" t="inlineStr">
@@ -59883,11 +59848,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U320" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA320" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -59900,7 +59860,7 @@
       </c>
       <c r="AP320" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ320" t="inlineStr">
@@ -59910,15 +59870,15 @@
       </c>
       <c r="AS320" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT320" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU320" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV320" t="inlineStr">
@@ -60134,7 +60094,7 @@
       </c>
       <c r="AP321" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ321" t="inlineStr">
@@ -60144,15 +60104,15 @@
       </c>
       <c r="AS321" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT321" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU321" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV321" t="inlineStr">
@@ -67016,11 +66976,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA357" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -67033,7 +66988,7 @@
       </c>
       <c r="AP357" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ357" t="inlineStr">
@@ -67043,15 +66998,15 @@
       </c>
       <c r="AS357" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT357" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU357" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV357" t="inlineStr">
@@ -67267,7 +67222,7 @@
       </c>
       <c r="AP358" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ358" t="inlineStr">
@@ -67277,15 +67232,15 @@
       </c>
       <c r="AS358" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT358" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU358" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV358" t="inlineStr">
@@ -73374,11 +73329,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA390" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -73391,7 +73341,7 @@
       </c>
       <c r="AP390" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ390" t="inlineStr">
@@ -73401,15 +73351,15 @@
       </c>
       <c r="AS390" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT390" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU390" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV390" t="inlineStr">
@@ -73625,7 +73575,7 @@
       </c>
       <c r="AP391" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ391" t="inlineStr">
@@ -73635,15 +73585,15 @@
       </c>
       <c r="AS391" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT391" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU391" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV391" t="inlineStr">
@@ -80502,11 +80452,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA427" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -80519,7 +80464,7 @@
       </c>
       <c r="AP427" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ427" t="inlineStr">
@@ -80529,15 +80474,15 @@
       </c>
       <c r="AS427" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT427" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU427" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV427" t="inlineStr">
@@ -80753,7 +80698,7 @@
       </c>
       <c r="AP428" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ428" t="inlineStr">
@@ -80763,15 +80708,15 @@
       </c>
       <c r="AS428" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT428" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU428" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV428" t="inlineStr">

--- a/diseases/d043/2000-2004.xlsx
+++ b/diseases/d043/2000-2004.xlsx
@@ -7869,9 +7869,12 @@
       <c r="O50" t="n">
         <v>3</v>
       </c>
+      <c r="R50" t="n">
+        <v>0.003292723081988804</v>
+      </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -8254,9 +8257,12 @@
       <c r="O52" t="n">
         <v>1</v>
       </c>
+      <c r="R52" t="n">
+        <v>0.002045408058907752</v>
+      </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -8644,9 +8650,12 @@
       <c r="O54" t="n">
         <v>93</v>
       </c>
+      <c r="R54" t="n">
+        <v>0.1365839330298135</v>
+      </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -9034,9 +9043,12 @@
       <c r="O56" t="n">
         <v>1</v>
       </c>
+      <c r="R56" t="n">
+        <v>0.01222493887530562</v>
+      </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -9424,9 +9436,12 @@
       <c r="O58" t="n">
         <v>17</v>
       </c>
+      <c r="R58" t="n">
+        <v>0.04031301873369694</v>
+      </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -9809,9 +9824,12 @@
       <c r="O60" t="n">
         <v>3</v>
       </c>
+      <c r="R60" t="n">
+        <v>0.01253656498119515</v>
+      </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -10199,9 +10217,12 @@
       <c r="O62" t="n">
         <v>1</v>
       </c>
+      <c r="R62" t="n">
+        <v>0.001236093943139679</v>
+      </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -10584,9 +10605,12 @@
       <c r="O64" t="n">
         <v>19</v>
       </c>
+      <c r="R64" t="n">
+        <v>0.02069716775599128</v>
+      </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -10969,9 +10993,12 @@
       <c r="O66" t="n">
         <v>4</v>
       </c>
+      <c r="R66" t="n">
+        <v>0.010866612333605</v>
+      </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -11359,9 +11386,12 @@
       <c r="O68" t="n">
         <v>14</v>
       </c>
+      <c r="R68" t="n">
+        <v>0.04197901049475262</v>
+      </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -11749,9 +11779,12 @@
       <c r="O70" t="n">
         <v>15</v>
       </c>
+      <c r="R70" t="n">
+        <v>0.146484375</v>
+      </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -12139,9 +12172,12 @@
       <c r="O72" t="n">
         <v>24</v>
       </c>
+      <c r="R72" t="n">
+        <v>0.05436013590033975</v>
+      </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -12677,9 +12713,12 @@
       <c r="O75" t="n">
         <v>1</v>
       </c>
+      <c r="R75" t="n">
+        <v>0.006697923643670462</v>
+      </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -13067,9 +13106,12 @@
       <c r="O77" t="n">
         <v>4</v>
       </c>
+      <c r="R77" t="n">
+        <v>0.01133465570983281</v>
+      </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -13452,9 +13494,12 @@
       <c r="O79" t="n">
         <v>7</v>
       </c>
+      <c r="R79" t="n">
+        <v>0.007683020524640544</v>
+      </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -13837,9 +13882,12 @@
       <c r="O81" t="n">
         <v>2</v>
       </c>
+      <c r="R81" t="n">
+        <v>0.004090816117815504</v>
+      </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -14227,9 +14275,12 @@
       <c r="O83" t="n">
         <v>2</v>
       </c>
+      <c r="R83" t="n">
+        <v>0.002058248430585571</v>
+      </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -14612,9 +14663,12 @@
       <c r="O85" t="n">
         <v>96</v>
       </c>
+      <c r="R85" t="n">
+        <v>0.1409898663533559</v>
+      </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -15002,9 +15056,12 @@
       <c r="O87" t="n">
         <v>3</v>
       </c>
+      <c r="R87" t="n">
+        <v>0.03667481662591687</v>
+      </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -15392,9 +15449,12 @@
       <c r="O89" t="n">
         <v>1</v>
       </c>
+      <c r="R89" t="n">
+        <v>0.001492982979994028</v>
+      </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -15777,9 +15837,12 @@
       <c r="O91" t="n">
         <v>1</v>
       </c>
+      <c r="R91" t="n">
+        <v>0.003691399040236249</v>
+      </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -16167,9 +16230,12 @@
       <c r="O93" t="n">
         <v>23</v>
       </c>
+      <c r="R93" t="n">
+        <v>0.0545411429926488</v>
+      </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -16552,9 +16618,12 @@
       <c r="O95" t="n">
         <v>5</v>
       </c>
+      <c r="R95" t="n">
+        <v>0.02089427496865859</v>
+      </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -16942,9 +17011,12 @@
       <c r="O97" t="n">
         <v>7</v>
       </c>
+      <c r="R97" t="n">
+        <v>0.00865265760197775</v>
+      </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -17327,9 +17399,12 @@
       <c r="O99" t="n">
         <v>16</v>
       </c>
+      <c r="R99" t="n">
+        <v>0.01742919389978214</v>
+      </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -17712,9 +17787,12 @@
       <c r="O101" t="n">
         <v>2</v>
       </c>
+      <c r="R101" t="n">
+        <v>0.005433306166802499</v>
+      </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -18102,9 +18180,12 @@
       <c r="O103" t="n">
         <v>10</v>
       </c>
+      <c r="R103" t="n">
+        <v>0.02998500749625187</v>
+      </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -18492,9 +18573,12 @@
       <c r="O105" t="n">
         <v>6</v>
       </c>
+      <c r="R105" t="n">
+        <v>0.05859374999999999</v>
+      </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -18882,9 +18966,12 @@
       <c r="O107" t="n">
         <v>28</v>
       </c>
+      <c r="R107" t="n">
+        <v>0.06342015855039637</v>
+      </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -19420,9 +19507,12 @@
       <c r="O110" t="n">
         <v>3</v>
       </c>
+      <c r="R110" t="n">
+        <v>0.008500991782374611</v>
+      </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -19805,9 +19895,12 @@
       <c r="O112" t="n">
         <v>4</v>
       </c>
+      <c r="R112" t="n">
+        <v>0.00439029744265174</v>
+      </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -20190,9 +20283,12 @@
       <c r="O114" t="n">
         <v>2</v>
       </c>
+      <c r="R114" t="n">
+        <v>0.004090816117815504</v>
+      </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -20580,9 +20676,12 @@
       <c r="O116" t="n">
         <v>2</v>
       </c>
+      <c r="R116" t="n">
+        <v>0.002058248430585571</v>
+      </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -20965,9 +21064,12 @@
       <c r="O118" t="n">
         <v>122</v>
       </c>
+      <c r="R118" t="n">
+        <v>0.1791746218240564</v>
+      </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -21355,9 +21457,12 @@
       <c r="O120" t="n">
         <v>1</v>
       </c>
+      <c r="R120" t="n">
+        <v>0.001492982979994028</v>
+      </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -21740,9 +21845,12 @@
       <c r="O122" t="n">
         <v>28</v>
       </c>
+      <c r="R122" t="n">
+        <v>0.06639791320844202</v>
+      </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -22125,9 +22233,12 @@
       <c r="O124" t="n">
         <v>5</v>
       </c>
+      <c r="R124" t="n">
+        <v>0.02089427496865859</v>
+      </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
@@ -22515,9 +22626,12 @@
       <c r="O126" t="n">
         <v>5</v>
       </c>
+      <c r="R126" t="n">
+        <v>0.006180469715698393</v>
+      </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -22900,9 +23014,12 @@
       <c r="O128" t="n">
         <v>4</v>
       </c>
+      <c r="R128" t="n">
+        <v>0.004357298474945534</v>
+      </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -23285,9 +23402,12 @@
       <c r="O130" t="n">
         <v>7</v>
       </c>
+      <c r="R130" t="n">
+        <v>0.01901657158380875</v>
+      </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
@@ -23675,9 +23795,12 @@
       <c r="O132" t="n">
         <v>11</v>
       </c>
+      <c r="R132" t="n">
+        <v>0.03298350824587706</v>
+      </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -24065,9 +24188,12 @@
       <c r="O134" t="n">
         <v>5</v>
       </c>
+      <c r="R134" t="n">
+        <v>0.048828125</v>
+      </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
@@ -24455,9 +24581,12 @@
       <c r="O136" t="n">
         <v>1</v>
       </c>
+      <c r="R136" t="n">
+        <v>0.005094243504839531</v>
+      </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -24840,9 +24969,12 @@
       <c r="O138" t="n">
         <v>41</v>
       </c>
+      <c r="R138" t="n">
+        <v>0.09286523216308042</v>
+      </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U138" t="inlineStr">
@@ -25378,9 +25510,12 @@
       <c r="O141" t="n">
         <v>3</v>
       </c>
+      <c r="R141" t="n">
+        <v>0.02009377093101139</v>
+      </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
@@ -25768,9 +25903,12 @@
       <c r="O143" t="n">
         <v>2</v>
       </c>
+      <c r="R143" t="n">
+        <v>0.005667327854916407</v>
+      </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -26153,9 +26291,12 @@
       <c r="O145" t="n">
         <v>6</v>
       </c>
+      <c r="R145" t="n">
+        <v>0.006585446163977608</v>
+      </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -26538,9 +26679,12 @@
       <c r="O147" t="n">
         <v>2</v>
       </c>
+      <c r="R147" t="n">
+        <v>0.007870916961826053</v>
+      </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -26923,9 +27067,12 @@
       <c r="O149" t="n">
         <v>6</v>
       </c>
+      <c r="R149" t="n">
+        <v>0.01227244835344651</v>
+      </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U149" t="inlineStr">
@@ -27313,9 +27460,12 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
+      <c r="R151" t="n">
+        <v>0.002561475409836065</v>
+      </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U151" t="inlineStr">
@@ -27703,9 +27853,12 @@
       <c r="O153" t="n">
         <v>2</v>
       </c>
+      <c r="R153" t="n">
+        <v>0.002058248430585571</v>
+      </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -28088,9 +28241,12 @@
       <c r="O155" t="n">
         <v>115</v>
       </c>
+      <c r="R155" t="n">
+        <v>0.1688941107357909</v>
+      </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U155" t="inlineStr">
@@ -28478,9 +28634,12 @@
       <c r="O157" t="n">
         <v>2</v>
       </c>
+      <c r="R157" t="n">
+        <v>0.02444987775061125</v>
+      </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U157" t="inlineStr">
@@ -28868,9 +29027,12 @@
       <c r="O159" t="n">
         <v>2</v>
       </c>
+      <c r="R159" t="n">
+        <v>0.005239717055279015</v>
+      </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U159" t="inlineStr">
@@ -29258,9 +29420,12 @@
       <c r="O161" t="n">
         <v>1</v>
       </c>
+      <c r="R161" t="n">
+        <v>0.001492982979994028</v>
+      </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -29643,9 +29808,12 @@
       <c r="O163" t="n">
         <v>19</v>
       </c>
+      <c r="R163" t="n">
+        <v>0.04505572682001423</v>
+      </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -30028,9 +30196,12 @@
       <c r="O165" t="n">
         <v>12</v>
       </c>
+      <c r="R165" t="n">
+        <v>0.05014625992478061</v>
+      </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U165" t="inlineStr">
@@ -30418,9 +30589,12 @@
       <c r="O167" t="n">
         <v>8</v>
       </c>
+      <c r="R167" t="n">
+        <v>0.009888751545117428</v>
+      </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -30803,9 +30977,12 @@
       <c r="O169" t="n">
         <v>12</v>
       </c>
+      <c r="R169" t="n">
+        <v>0.0130718954248366</v>
+      </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -31188,9 +31365,12 @@
       <c r="O171" t="n">
         <v>2</v>
       </c>
+      <c r="R171" t="n">
+        <v>0.005433306166802499</v>
+      </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U171" t="inlineStr">
@@ -31578,9 +31758,12 @@
       <c r="O173" t="n">
         <v>11</v>
       </c>
+      <c r="R173" t="n">
+        <v>0.03298350824587706</v>
+      </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U173" t="inlineStr">
@@ -31968,9 +32151,12 @@
       <c r="O175" t="n">
         <v>5</v>
       </c>
+      <c r="R175" t="n">
+        <v>0.048828125</v>
+      </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U175" t="inlineStr">
@@ -32358,9 +32544,12 @@
       <c r="O177" t="n">
         <v>1</v>
       </c>
+      <c r="R177" t="n">
+        <v>0.005094243504839531</v>
+      </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -32743,9 +32932,12 @@
       <c r="O179" t="n">
         <v>45</v>
       </c>
+      <c r="R179" t="n">
+        <v>0.101925254813137</v>
+      </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U179" t="inlineStr">
@@ -33281,9 +33473,12 @@
       <c r="O182" t="n">
         <v>3</v>
       </c>
+      <c r="R182" t="n">
+        <v>0.02009377093101139</v>
+      </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U182" t="inlineStr">
@@ -33671,9 +33866,12 @@
       <c r="O184" t="n">
         <v>1</v>
       </c>
+      <c r="R184" t="n">
+        <v>0.003580379520229144</v>
+      </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -34056,9 +34254,12 @@
       <c r="O186" t="n">
         <v>4</v>
       </c>
+      <c r="R186" t="n">
+        <v>0.01133465570983281</v>
+      </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -34441,9 +34642,12 @@
       <c r="O188" t="n">
         <v>9</v>
       </c>
+      <c r="R188" t="n">
+        <v>0.009878169245966415</v>
+      </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -34826,9 +35030,12 @@
       <c r="O190" t="n">
         <v>3</v>
       </c>
+      <c r="R190" t="n">
+        <v>0.006136224176723256</v>
+      </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U190" t="inlineStr">
@@ -35216,9 +35423,12 @@
       <c r="O192" t="n">
         <v>2</v>
       </c>
+      <c r="R192" t="n">
+        <v>0.002058248430585571</v>
+      </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -35601,9 +35811,12 @@
       <c r="O194" t="n">
         <v>117</v>
       </c>
+      <c r="R194" t="n">
+        <v>0.1718313996181524</v>
+      </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U194" t="inlineStr">
@@ -35991,9 +36204,12 @@
       <c r="O196" t="n">
         <v>6</v>
       </c>
+      <c r="R196" t="n">
+        <v>0.07334963325183375</v>
+      </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U196" t="inlineStr">
@@ -36381,9 +36597,12 @@
       <c r="O198" t="n">
         <v>23</v>
       </c>
+      <c r="R198" t="n">
+        <v>0.0545411429926488</v>
+      </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -36766,9 +36985,12 @@
       <c r="O200" t="n">
         <v>2</v>
       </c>
+      <c r="R200" t="n">
+        <v>0.008357709987463435</v>
+      </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U200" t="inlineStr">
@@ -37156,9 +37378,12 @@
       <c r="O202" t="n">
         <v>5</v>
       </c>
+      <c r="R202" t="n">
+        <v>0.006180469715698393</v>
+      </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -37541,9 +37766,12 @@
       <c r="O204" t="n">
         <v>16</v>
       </c>
+      <c r="R204" t="n">
+        <v>0.01742919389978214</v>
+      </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -37926,9 +38154,12 @@
       <c r="O206" t="n">
         <v>4</v>
       </c>
+      <c r="R206" t="n">
+        <v>0.010866612333605</v>
+      </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U206" t="inlineStr">
@@ -38316,9 +38547,12 @@
       <c r="O208" t="n">
         <v>15</v>
       </c>
+      <c r="R208" t="n">
+        <v>0.04497751124437781</v>
+      </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U208" t="inlineStr">
@@ -38706,9 +38940,12 @@
       <c r="O210" t="n">
         <v>6</v>
       </c>
+      <c r="R210" t="n">
+        <v>0.05859374999999999</v>
+      </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U210" t="inlineStr">
@@ -39096,9 +39333,12 @@
       <c r="O212" t="n">
         <v>73</v>
       </c>
+      <c r="R212" t="n">
+        <v>0.1653454133635334</v>
+      </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
@@ -39486,9 +39726,12 @@
       <c r="O214" t="n">
         <v>2</v>
       </c>
+      <c r="R214" t="n">
+        <v>0.004060913705583756</v>
+      </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -40019,9 +40262,12 @@
       <c r="O217" t="n">
         <v>4</v>
       </c>
+      <c r="R217" t="n">
+        <v>0.01133465570983281</v>
+      </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -40404,9 +40650,12 @@
       <c r="O219" t="n">
         <v>11</v>
       </c>
+      <c r="R219" t="n">
+        <v>0.01207331796729228</v>
+      </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -40789,9 +41038,12 @@
       <c r="O221" t="n">
         <v>16</v>
       </c>
+      <c r="R221" t="n">
+        <v>0.03272652894252404</v>
+      </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U221" t="inlineStr">
@@ -41179,9 +41431,12 @@
       <c r="O223" t="n">
         <v>4</v>
       </c>
+      <c r="R223" t="n">
+        <v>0.004116496861171143</v>
+      </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -41564,9 +41819,12 @@
       <c r="O225" t="n">
         <v>98</v>
       </c>
+      <c r="R225" t="n">
+        <v>0.1439271552357174</v>
+      </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U225" t="inlineStr">
@@ -41954,9 +42212,12 @@
       <c r="O227" t="n">
         <v>5</v>
       </c>
+      <c r="R227" t="n">
+        <v>0.06112469437652811</v>
+      </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U227" t="inlineStr">
@@ -42344,9 +42605,12 @@
       <c r="O229" t="n">
         <v>1</v>
       </c>
+      <c r="R229" t="n">
+        <v>0.001492982979994028</v>
+      </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -42729,9 +42993,12 @@
       <c r="O231" t="n">
         <v>13</v>
       </c>
+      <c r="R231" t="n">
+        <v>0.03082760256106237</v>
+      </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -43114,9 +43381,12 @@
       <c r="O233" t="n">
         <v>2</v>
       </c>
+      <c r="R233" t="n">
+        <v>0.008357709987463435</v>
+      </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U233" t="inlineStr">
@@ -43504,9 +43774,12 @@
       <c r="O235" t="n">
         <v>8</v>
       </c>
+      <c r="R235" t="n">
+        <v>0.009888751545117428</v>
+      </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -43889,9 +44162,12 @@
       <c r="O237" t="n">
         <v>22</v>
       </c>
+      <c r="R237" t="n">
+        <v>0.02396514161220044</v>
+      </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -44274,9 +44550,12 @@
       <c r="O239" t="n">
         <v>4</v>
       </c>
+      <c r="R239" t="n">
+        <v>0.010866612333605</v>
+      </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U239" t="inlineStr">
@@ -44664,9 +44943,12 @@
       <c r="O241" t="n">
         <v>22</v>
       </c>
+      <c r="R241" t="n">
+        <v>0.06596701649175413</v>
+      </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U241" t="inlineStr">
@@ -45054,9 +45336,12 @@
       <c r="O243" t="n">
         <v>4</v>
       </c>
+      <c r="R243" t="n">
+        <v>0.0390625</v>
+      </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U243" t="inlineStr">
@@ -45444,9 +45729,12 @@
       <c r="O245" t="n">
         <v>88</v>
       </c>
+      <c r="R245" t="n">
+        <v>0.1993204983012458</v>
+      </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U245" t="inlineStr">
@@ -45982,9 +46270,12 @@
       <c r="O248" t="n">
         <v>1</v>
       </c>
+      <c r="R248" t="n">
+        <v>0.003580379520229144</v>
+      </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -46367,9 +46658,12 @@
       <c r="O250" t="n">
         <v>9</v>
       </c>
+      <c r="R250" t="n">
+        <v>0.02550297534712383</v>
+      </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -46752,9 +47046,12 @@
       <c r="O252" t="n">
         <v>15</v>
       </c>
+      <c r="R252" t="n">
+        <v>0.01646361540994402</v>
+      </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -47137,9 +47434,12 @@
       <c r="O254" t="n">
         <v>14</v>
       </c>
+      <c r="R254" t="n">
+        <v>0.02863571282470853</v>
+      </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U254" t="inlineStr">
@@ -47527,9 +47827,12 @@
       <c r="O256" t="n">
         <v>1</v>
       </c>
+      <c r="R256" t="n">
+        <v>0.002561475409836065</v>
+      </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U256" t="inlineStr">
@@ -47917,9 +48220,12 @@
       <c r="O258" t="n">
         <v>6</v>
       </c>
+      <c r="R258" t="n">
+        <v>0.006174745291756716</v>
+      </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -48302,9 +48608,12 @@
       <c r="O260" t="n">
         <v>117</v>
       </c>
+      <c r="R260" t="n">
+        <v>0.1718313996181524</v>
+      </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U260" t="inlineStr">
@@ -48692,9 +49001,12 @@
       <c r="O262" t="n">
         <v>8</v>
       </c>
+      <c r="R262" t="n">
+        <v>0.09779951100244498</v>
+      </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U262" t="inlineStr">
@@ -49082,9 +49394,12 @@
       <c r="O264" t="n">
         <v>1</v>
       </c>
+      <c r="R264" t="n">
+        <v>0.001492982979994028</v>
+      </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
@@ -49467,9 +49782,12 @@
       <c r="O266" t="n">
         <v>20</v>
       </c>
+      <c r="R266" t="n">
+        <v>0.04742708086317287</v>
+      </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
@@ -49852,9 +50170,12 @@
       <c r="O268" t="n">
         <v>8</v>
       </c>
+      <c r="R268" t="n">
+        <v>0.03343083994985374</v>
+      </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U268" t="inlineStr">
@@ -50242,9 +50563,12 @@
       <c r="O270" t="n">
         <v>16</v>
       </c>
+      <c r="R270" t="n">
+        <v>0.01977750309023486</v>
+      </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -50627,9 +50951,12 @@
       <c r="O272" t="n">
         <v>10</v>
       </c>
+      <c r="R272" t="n">
+        <v>0.01089324618736384</v>
+      </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -51012,9 +51339,12 @@
       <c r="O274" t="n">
         <v>3</v>
       </c>
+      <c r="R274" t="n">
+        <v>0.008149959250203748</v>
+      </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U274" t="inlineStr">
@@ -51402,9 +51732,12 @@
       <c r="O276" t="n">
         <v>30</v>
       </c>
+      <c r="R276" t="n">
+        <v>0.08995502248875563</v>
+      </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U276" t="inlineStr">
@@ -51792,9 +52125,12 @@
       <c r="O278" t="n">
         <v>5</v>
       </c>
+      <c r="R278" t="n">
+        <v>0.048828125</v>
+      </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U278" t="inlineStr">
@@ -52182,9 +52518,12 @@
       <c r="O280" t="n">
         <v>168</v>
       </c>
+      <c r="R280" t="n">
+        <v>0.3805209513023783</v>
+      </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U280" t="inlineStr">
@@ -52720,9 +53059,12 @@
       <c r="O283" t="n">
         <v>3</v>
       </c>
+      <c r="R283" t="n">
+        <v>0.02009377093101139</v>
+      </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U283" t="inlineStr">
@@ -53110,9 +53452,12 @@
       <c r="O285" t="n">
         <v>1</v>
       </c>
+      <c r="R285" t="n">
+        <v>0.003580379520229144</v>
+      </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -53495,9 +53840,12 @@
       <c r="O287" t="n">
         <v>6</v>
       </c>
+      <c r="R287" t="n">
+        <v>0.01700198356474922</v>
+      </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -53880,9 +54228,12 @@
       <c r="O289" t="n">
         <v>12</v>
       </c>
+      <c r="R289" t="n">
+        <v>0.01317089232795522</v>
+      </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -54265,9 +54616,12 @@
       <c r="O291" t="n">
         <v>10</v>
       </c>
+      <c r="R291" t="n">
+        <v>0.02045408058907752</v>
+      </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U291" t="inlineStr">
@@ -54655,9 +55009,12 @@
       <c r="O293" t="n">
         <v>7</v>
       </c>
+      <c r="R293" t="n">
+        <v>0.007203869507049501</v>
+      </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -55040,9 +55397,12 @@
       <c r="O295" t="n">
         <v>96</v>
       </c>
+      <c r="R295" t="n">
+        <v>0.1409898663533559</v>
+      </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U295" t="inlineStr">
@@ -55430,9 +55790,12 @@
       <c r="O297" t="n">
         <v>7</v>
       </c>
+      <c r="R297" t="n">
+        <v>0.08557457212713937</v>
+      </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U297" t="inlineStr">
@@ -55820,9 +56183,12 @@
       <c r="O299" t="n">
         <v>1</v>
       </c>
+      <c r="R299" t="n">
+        <v>0.001492982979994028</v>
+      </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -56205,9 +56571,12 @@
       <c r="O301" t="n">
         <v>41</v>
       </c>
+      <c r="R301" t="n">
+        <v>0.09722551576950439</v>
+      </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -56590,9 +56959,12 @@
       <c r="O303" t="n">
         <v>8</v>
       </c>
+      <c r="R303" t="n">
+        <v>0.03343083994985374</v>
+      </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U303" t="inlineStr">
@@ -56980,9 +57352,12 @@
       <c r="O305" t="n">
         <v>27</v>
       </c>
+      <c r="R305" t="n">
+        <v>0.03337453646477132</v>
+      </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -57365,9 +57740,12 @@
       <c r="O307" t="n">
         <v>12</v>
       </c>
+      <c r="R307" t="n">
+        <v>0.0130718954248366</v>
+      </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -57750,9 +58128,12 @@
       <c r="O309" t="n">
         <v>4</v>
       </c>
+      <c r="R309" t="n">
+        <v>0.010866612333605</v>
+      </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U309" t="inlineStr">
@@ -58140,9 +58521,12 @@
       <c r="O311" t="n">
         <v>37</v>
       </c>
+      <c r="R311" t="n">
+        <v>0.1109445277361319</v>
+      </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U311" t="inlineStr">
@@ -58530,9 +58914,12 @@
       <c r="O313" t="n">
         <v>10</v>
       </c>
+      <c r="R313" t="n">
+        <v>0.09765625</v>
+      </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U313" t="inlineStr">
@@ -58920,9 +59307,12 @@
       <c r="O315" t="n">
         <v>101</v>
       </c>
+      <c r="R315" t="n">
+        <v>0.2287655719139298</v>
+      </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U315" t="inlineStr">
@@ -59458,9 +59848,12 @@
       <c r="O318" t="n">
         <v>1</v>
       </c>
+      <c r="R318" t="n">
+        <v>0.003580379520229144</v>
+      </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -59843,9 +60236,12 @@
       <c r="O320" t="n">
         <v>9</v>
       </c>
+      <c r="R320" t="n">
+        <v>0.02550297534712383</v>
+      </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -60228,9 +60624,12 @@
       <c r="O322" t="n">
         <v>10</v>
       </c>
+      <c r="R322" t="n">
+        <v>0.01097574360662935</v>
+      </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -60613,9 +61012,12 @@
       <c r="O324" t="n">
         <v>7</v>
       </c>
+      <c r="R324" t="n">
+        <v>0.01431785641235426</v>
+      </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U324" t="inlineStr">
@@ -61003,9 +61405,12 @@
       <c r="O326" t="n">
         <v>1</v>
       </c>
+      <c r="R326" t="n">
+        <v>0.002561475409836065</v>
+      </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U326" t="inlineStr">
@@ -61393,9 +61798,12 @@
       <c r="O328" t="n">
         <v>4</v>
       </c>
+      <c r="R328" t="n">
+        <v>0.004116496861171143</v>
+      </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -61778,9 +62186,12 @@
       <c r="O330" t="n">
         <v>100</v>
       </c>
+      <c r="R330" t="n">
+        <v>0.146864444118079</v>
+      </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U330" t="inlineStr">
@@ -62168,9 +62579,12 @@
       <c r="O332" t="n">
         <v>4</v>
       </c>
+      <c r="R332" t="n">
+        <v>0.04889975550122249</v>
+      </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U332" t="inlineStr">
@@ -62558,9 +62972,12 @@
       <c r="O334" t="n">
         <v>71</v>
       </c>
+      <c r="R334" t="n">
+        <v>0.1683661370642637</v>
+      </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -62943,9 +63360,12 @@
       <c r="O336" t="n">
         <v>5</v>
       </c>
+      <c r="R336" t="n">
+        <v>0.02089427496865859</v>
+      </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U336" t="inlineStr">
@@ -63333,9 +63753,12 @@
       <c r="O338" t="n">
         <v>16</v>
       </c>
+      <c r="R338" t="n">
+        <v>0.01977750309023486</v>
+      </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -63718,9 +64141,12 @@
       <c r="O340" t="n">
         <v>18</v>
       </c>
+      <c r="R340" t="n">
+        <v>0.0196078431372549</v>
+      </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -64103,9 +64529,12 @@
       <c r="O342" t="n">
         <v>3</v>
       </c>
+      <c r="R342" t="n">
+        <v>0.008149959250203748</v>
+      </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U342" t="inlineStr">
@@ -64493,9 +64922,12 @@
       <c r="O344" t="n">
         <v>29</v>
       </c>
+      <c r="R344" t="n">
+        <v>0.08695652173913043</v>
+      </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U344" t="inlineStr">
@@ -64883,9 +65315,12 @@
       <c r="O346" t="n">
         <v>9</v>
       </c>
+      <c r="R346" t="n">
+        <v>0.087890625</v>
+      </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U346" t="inlineStr">
@@ -65273,9 +65708,12 @@
       <c r="O348" t="n">
         <v>96</v>
       </c>
+      <c r="R348" t="n">
+        <v>0.217440543601359</v>
+      </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U348" t="inlineStr">
@@ -65663,9 +66101,12 @@
       <c r="O350" t="n">
         <v>1</v>
       </c>
+      <c r="R350" t="n">
+        <v>0.002030456852791878</v>
+      </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA350" t="inlineStr">
@@ -66196,9 +66637,12 @@
       <c r="O353" t="n">
         <v>1</v>
       </c>
+      <c r="R353" t="n">
+        <v>0.006697923643670462</v>
+      </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U353" t="inlineStr">
@@ -66586,9 +67030,12 @@
       <c r="O355" t="n">
         <v>1</v>
       </c>
+      <c r="R355" t="n">
+        <v>0.003580379520229144</v>
+      </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
@@ -66971,9 +67418,12 @@
       <c r="O357" t="n">
         <v>7</v>
       </c>
+      <c r="R357" t="n">
+        <v>0.01983564749220743</v>
+      </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
@@ -67356,9 +67806,12 @@
       <c r="O359" t="n">
         <v>11</v>
       </c>
+      <c r="R359" t="n">
+        <v>0.01207331796729228</v>
+      </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
@@ -67741,9 +68194,12 @@
       <c r="O361" t="n">
         <v>1</v>
       </c>
+      <c r="R361" t="n">
+        <v>0.003935458480913027</v>
+      </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA361" t="inlineStr">
@@ -68126,9 +68582,12 @@
       <c r="O363" t="n">
         <v>11</v>
       </c>
+      <c r="R363" t="n">
+        <v>0.02249948864798527</v>
+      </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U363" t="inlineStr">
@@ -68516,9 +68975,12 @@
       <c r="O365" t="n">
         <v>2</v>
       </c>
+      <c r="R365" t="n">
+        <v>0.005122950819672131</v>
+      </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U365" t="inlineStr">
@@ -68906,9 +69368,12 @@
       <c r="O367" t="n">
         <v>208</v>
       </c>
+      <c r="R367" t="n">
+        <v>0.3054780437656043</v>
+      </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U367" t="inlineStr">
@@ -69296,9 +69761,12 @@
       <c r="O369" t="n">
         <v>4</v>
       </c>
+      <c r="R369" t="n">
+        <v>0.04889975550122249</v>
+      </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U369" t="inlineStr">
@@ -69686,9 +70154,12 @@
       <c r="O371" t="n">
         <v>1</v>
       </c>
+      <c r="R371" t="n">
+        <v>0.001492982979994028</v>
+      </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA371" t="inlineStr">
@@ -70071,9 +70542,12 @@
       <c r="O373" t="n">
         <v>173</v>
       </c>
+      <c r="R373" t="n">
+        <v>0.4102442494664453</v>
+      </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
@@ -70456,9 +70930,12 @@
       <c r="O375" t="n">
         <v>13</v>
       </c>
+      <c r="R375" t="n">
+        <v>0.05432511491851233</v>
+      </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U375" t="inlineStr">
@@ -70846,9 +71323,12 @@
       <c r="O377" t="n">
         <v>8</v>
       </c>
+      <c r="R377" t="n">
+        <v>0.009888751545117428</v>
+      </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
@@ -71231,9 +71711,12 @@
       <c r="O379" t="n">
         <v>132</v>
       </c>
+      <c r="R379" t="n">
+        <v>0.1437908496732026</v>
+      </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
@@ -71616,9 +72099,12 @@
       <c r="O381" t="n">
         <v>6</v>
       </c>
+      <c r="R381" t="n">
+        <v>0.0162999185004075</v>
+      </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U381" t="inlineStr">
@@ -72006,9 +72492,12 @@
       <c r="O383" t="n">
         <v>41</v>
       </c>
+      <c r="R383" t="n">
+        <v>0.1229385307346327</v>
+      </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U383" t="inlineStr">
@@ -72396,9 +72885,12 @@
       <c r="O385" t="n">
         <v>51</v>
       </c>
+      <c r="R385" t="n">
+        <v>0.4980468750000001</v>
+      </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U385" t="inlineStr">
@@ -72786,9 +73278,12 @@
       <c r="O387" t="n">
         <v>68</v>
       </c>
+      <c r="R387" t="n">
+        <v>0.1540203850509626</v>
+      </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U387" t="inlineStr">
@@ -73324,9 +73819,12 @@
       <c r="O390" t="n">
         <v>2</v>
       </c>
+      <c r="R390" t="n">
+        <v>0.005667327854916407</v>
+      </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
@@ -73709,9 +74207,12 @@
       <c r="O392" t="n">
         <v>6</v>
       </c>
+      <c r="R392" t="n">
+        <v>0.006585446163977608</v>
+      </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA392" t="inlineStr">
@@ -74094,9 +74595,12 @@
       <c r="O394" t="n">
         <v>2</v>
       </c>
+      <c r="R394" t="n">
+        <v>0.007870916961826053</v>
+      </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA394" t="inlineStr">
@@ -74479,9 +74983,12 @@
       <c r="O396" t="n">
         <v>8</v>
       </c>
+      <c r="R396" t="n">
+        <v>0.01636326447126202</v>
+      </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U396" t="inlineStr">
@@ -74869,9 +75376,12 @@
       <c r="O398" t="n">
         <v>1</v>
       </c>
+      <c r="R398" t="n">
+        <v>0.002561475409836065</v>
+      </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U398" t="inlineStr">
@@ -75259,9 +75769,12 @@
       <c r="O400" t="n">
         <v>1</v>
       </c>
+      <c r="R400" t="n">
+        <v>0.001029124215292786</v>
+      </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA400" t="inlineStr">
@@ -75644,9 +76157,12 @@
       <c r="O402" t="n">
         <v>161</v>
       </c>
+      <c r="R402" t="n">
+        <v>0.2364517550301072</v>
+      </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U402" t="inlineStr">
@@ -76034,9 +76550,12 @@
       <c r="O404" t="n">
         <v>3</v>
       </c>
+      <c r="R404" t="n">
+        <v>0.03667481662591687</v>
+      </c>
       <c r="S404" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U404" t="inlineStr">
@@ -76424,9 +76943,12 @@
       <c r="O406" t="n">
         <v>1</v>
       </c>
+      <c r="R406" t="n">
+        <v>0.001492982979994028</v>
+      </c>
       <c r="S406" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA406" t="inlineStr">
@@ -76809,9 +77331,12 @@
       <c r="O408" t="n">
         <v>188</v>
       </c>
+      <c r="R408" t="n">
+        <v>0.445814560113825</v>
+      </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA408" t="inlineStr">
@@ -77194,9 +77719,12 @@
       <c r="O410" t="n">
         <v>11</v>
       </c>
+      <c r="R410" t="n">
+        <v>0.04596740493104889</v>
+      </c>
       <c r="S410" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U410" t="inlineStr">
@@ -77584,9 +78112,12 @@
       <c r="O412" t="n">
         <v>3</v>
       </c>
+      <c r="R412" t="n">
+        <v>0.003708281829419036</v>
+      </c>
       <c r="S412" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA412" t="inlineStr">
@@ -77969,9 +78500,12 @@
       <c r="O414" t="n">
         <v>42</v>
       </c>
+      <c r="R414" t="n">
+        <v>0.04575163398692811</v>
+      </c>
       <c r="S414" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA414" t="inlineStr">
@@ -78354,9 +78888,12 @@
       <c r="O416" t="n">
         <v>8</v>
       </c>
+      <c r="R416" t="n">
+        <v>0.02173322466721</v>
+      </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U416" t="inlineStr">
@@ -78744,9 +79281,12 @@
       <c r="O418" t="n">
         <v>25</v>
       </c>
+      <c r="R418" t="n">
+        <v>0.07496251874062967</v>
+      </c>
       <c r="S418" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U418" t="inlineStr">
@@ -79134,9 +79674,12 @@
       <c r="O420" t="n">
         <v>10</v>
       </c>
+      <c r="R420" t="n">
+        <v>0.09765625</v>
+      </c>
       <c r="S420" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U420" t="inlineStr">
@@ -79524,9 +80067,12 @@
       <c r="O422" t="n">
         <v>40</v>
       </c>
+      <c r="R422" t="n">
+        <v>0.09060022650056625</v>
+      </c>
       <c r="S422" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U422" t="inlineStr">
@@ -80062,9 +80608,12 @@
       <c r="O425" t="n">
         <v>1</v>
       </c>
+      <c r="R425" t="n">
+        <v>0.003580379520229144</v>
+      </c>
       <c r="S425" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA425" t="inlineStr">
@@ -80447,9 +80996,12 @@
       <c r="O427" t="n">
         <v>5</v>
       </c>
+      <c r="R427" t="n">
+        <v>0.01416831963729102</v>
+      </c>
       <c r="S427" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA427" t="inlineStr">
@@ -80832,9 +81384,12 @@
       <c r="O429" t="n">
         <v>6</v>
       </c>
+      <c r="R429" t="n">
+        <v>0.006585446163977608</v>
+      </c>
       <c r="S429" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA429" t="inlineStr">
@@ -81217,9 +81772,12 @@
       <c r="O431" t="n">
         <v>1</v>
       </c>
+      <c r="R431" t="n">
+        <v>0.002045408058907752</v>
+      </c>
       <c r="S431" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U431" t="inlineStr">
@@ -81607,9 +82165,12 @@
       <c r="O433" t="n">
         <v>2</v>
       </c>
+      <c r="R433" t="n">
+        <v>0.005122950819672131</v>
+      </c>
       <c r="S433" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U433" t="inlineStr">
@@ -81997,9 +82558,12 @@
       <c r="O435" t="n">
         <v>2</v>
       </c>
+      <c r="R435" t="n">
+        <v>0.002058248430585571</v>
+      </c>
       <c r="S435" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA435" t="inlineStr">
@@ -82382,9 +82946,12 @@
       <c r="O437" t="n">
         <v>61</v>
       </c>
+      <c r="R437" t="n">
+        <v>0.08958731091202821</v>
+      </c>
       <c r="S437" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U437" t="inlineStr">
@@ -82772,9 +83339,12 @@
       <c r="O439" t="n">
         <v>5</v>
       </c>
+      <c r="R439" t="n">
+        <v>0.06112469437652811</v>
+      </c>
       <c r="S439" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U439" t="inlineStr">
@@ -83162,9 +83732,12 @@
       <c r="O441" t="n">
         <v>67</v>
       </c>
+      <c r="R441" t="n">
+        <v>0.1588807208916291</v>
+      </c>
       <c r="S441" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA441" t="inlineStr">
@@ -83547,9 +84120,12 @@
       <c r="O443" t="n">
         <v>3</v>
       </c>
+      <c r="R443" t="n">
+        <v>0.01253656498119515</v>
+      </c>
       <c r="S443" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U443" t="inlineStr">
@@ -83937,9 +84513,12 @@
       <c r="O445" t="n">
         <v>3</v>
       </c>
+      <c r="R445" t="n">
+        <v>0.003708281829419036</v>
+      </c>
       <c r="S445" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA445" t="inlineStr">
@@ -84322,9 +84901,12 @@
       <c r="O447" t="n">
         <v>19</v>
       </c>
+      <c r="R447" t="n">
+        <v>0.02069716775599128</v>
+      </c>
       <c r="S447" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA447" t="inlineStr">
@@ -84707,9 +85289,12 @@
       <c r="O449" t="n">
         <v>2</v>
       </c>
+      <c r="R449" t="n">
+        <v>0.005433306166802499</v>
+      </c>
       <c r="S449" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U449" t="inlineStr">
@@ -85097,9 +85682,12 @@
       <c r="O451" t="n">
         <v>9</v>
       </c>
+      <c r="R451" t="n">
+        <v>0.02698650674662669</v>
+      </c>
       <c r="S451" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U451" t="inlineStr">
@@ -85487,9 +86075,12 @@
       <c r="O453" t="n">
         <v>7</v>
       </c>
+      <c r="R453" t="n">
+        <v>0.068359375</v>
+      </c>
       <c r="S453" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U453" t="inlineStr">
@@ -85877,9 +86468,12 @@
       <c r="O455" t="n">
         <v>18</v>
       </c>
+      <c r="R455" t="n">
+        <v>0.04077010192525481</v>
+      </c>
       <c r="S455" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U455" t="inlineStr">

--- a/diseases/d043/2000-2004.xlsx
+++ b/diseases/d043/2000-2004.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4142,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4180,6 +4295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4328,6 +4448,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4476,6 +4601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4624,6 +4754,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4772,6 +4907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4920,6 +5060,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5068,6 +5213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5216,6 +5366,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5364,6 +5519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5512,6 +5672,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5660,6 +5825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5808,6 +5978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5956,6 +6131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6104,6 +6284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6252,6 +6437,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6400,6 +6590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6548,6 +6743,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6696,6 +6896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6844,6 +7049,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6992,6 +7202,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7140,6 +7355,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7288,6 +7508,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7436,6 +7661,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7584,6 +7814,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7732,6 +7967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12576,6 +12816,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19370,6 +19615,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25373,6 +25623,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33336,6 +33591,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40125,6 +40385,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46133,6 +46398,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52922,6 +53192,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59711,6 +59986,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO317" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66500,6 +66780,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO352" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73682,6 +73967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO389" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -80471,6 +80761,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA424" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO424" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -86870,6 +87165,11 @@
       <c r="S457" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA457" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO457" t="inlineStr">

--- a/diseases/d043/2000-2004.xlsx
+++ b/diseases/d043/2000-2004.xlsx
@@ -8505,11 +8505,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8522,7 +8517,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -8532,15 +8527,15 @@
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -8575,7 +8570,7 @@
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
@@ -8756,7 +8751,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
@@ -8766,15 +8761,15 @@
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -8809,7 +8804,7 @@
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
@@ -11634,11 +11629,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11651,7 +11641,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
@@ -11661,15 +11651,15 @@
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -11885,7 +11875,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
@@ -11895,15 +11885,15 @@
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -14135,11 +14125,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14152,7 +14137,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
@@ -14162,15 +14147,15 @@
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -14205,7 +14190,7 @@
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
@@ -14386,7 +14371,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
@@ -14396,15 +14381,15 @@
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -14439,7 +14424,7 @@
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
@@ -18433,11 +18418,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18450,7 +18430,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
@@ -18460,15 +18440,15 @@
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -18684,7 +18664,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
@@ -18694,15 +18674,15 @@
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -20541,11 +20521,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20558,7 +20533,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
@@ -20568,15 +20543,15 @@
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -20611,7 +20586,7 @@
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
@@ -20792,7 +20767,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
@@ -20802,15 +20777,15 @@
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -20845,7 +20820,7 @@
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
@@ -24053,11 +24028,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24070,7 +24040,7 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
@@ -24080,15 +24050,15 @@
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
@@ -24304,7 +24274,7 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
@@ -24314,15 +24284,15 @@
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
@@ -27330,11 +27300,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27347,7 +27312,7 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ149" t="inlineStr">
@@ -27357,15 +27322,15 @@
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
@@ -27400,7 +27365,7 @@
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
@@ -27581,7 +27546,7 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
@@ -27591,15 +27556,15 @@
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
@@ -27634,7 +27599,7 @@
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
@@ -27723,11 +27688,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27740,7 +27700,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
@@ -27750,15 +27710,15 @@
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
@@ -27974,7 +27934,7 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
@@ -27984,15 +27944,15 @@
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
@@ -29290,11 +29250,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29307,7 +29262,7 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ159" t="inlineStr">
@@ -29317,15 +29272,15 @@
       </c>
       <c r="AS159" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
@@ -29541,7 +29496,7 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ160" t="inlineStr">
@@ -29551,15 +29506,15 @@
       </c>
       <c r="AS160" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
@@ -32021,11 +31976,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32038,7 +31988,7 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
@@ -32048,15 +31998,15 @@
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
@@ -32272,7 +32222,7 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
@@ -32282,15 +32232,15 @@
       </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
@@ -35298,11 +35248,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35315,7 +35260,7 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ190" t="inlineStr">
@@ -35325,15 +35270,15 @@
       </c>
       <c r="AS190" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
@@ -35368,7 +35313,7 @@
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
@@ -35549,7 +35494,7 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ191" t="inlineStr">
@@ -35559,15 +35504,15 @@
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
@@ -35602,7 +35547,7 @@
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
@@ -38815,11 +38760,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -38832,7 +38772,7 @@
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ208" t="inlineStr">
@@ -38842,15 +38782,15 @@
       </c>
       <c r="AS208" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
@@ -39066,7 +39006,7 @@
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ209" t="inlineStr">
@@ -39076,15 +39016,15 @@
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
@@ -41311,11 +41251,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -41328,7 +41263,7 @@
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ221" t="inlineStr">
@@ -41338,15 +41273,15 @@
       </c>
       <c r="AS221" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
@@ -41381,7 +41316,7 @@
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
@@ -41562,7 +41497,7 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
@@ -41572,15 +41507,15 @@
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
@@ -41615,7 +41550,7 @@
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
@@ -45216,11 +45151,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -45233,7 +45163,7 @@
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ241" t="inlineStr">
@@ -45243,15 +45173,15 @@
       </c>
       <c r="AS241" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT241" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
@@ -45467,7 +45397,7 @@
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ242" t="inlineStr">
@@ -45477,15 +45407,15 @@
       </c>
       <c r="AS242" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT242" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
@@ -47712,11 +47642,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA254" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47729,7 +47654,7 @@
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ254" t="inlineStr">
@@ -47739,15 +47664,15 @@
       </c>
       <c r="AS254" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
@@ -47782,7 +47707,7 @@
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
@@ -47963,7 +47888,7 @@
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ255" t="inlineStr">
@@ -47973,15 +47898,15 @@
       </c>
       <c r="AS255" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
@@ -48016,7 +47941,7 @@
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
@@ -48105,11 +48030,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA256" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48122,7 +48042,7 @@
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ256" t="inlineStr">
@@ -48132,15 +48052,15 @@
       </c>
       <c r="AS256" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
@@ -48356,7 +48276,7 @@
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ257" t="inlineStr">
@@ -48366,15 +48286,15 @@
       </c>
       <c r="AS257" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
@@ -52010,11 +51930,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA276" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -52027,7 +51942,7 @@
       </c>
       <c r="AP276" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ276" t="inlineStr">
@@ -52037,15 +51952,15 @@
       </c>
       <c r="AS276" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV276" t="inlineStr">
@@ -52261,7 +52176,7 @@
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ277" t="inlineStr">
@@ -52271,15 +52186,15 @@
       </c>
       <c r="AS277" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT277" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
@@ -54899,11 +54814,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA291" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -54916,7 +54826,7 @@
       </c>
       <c r="AP291" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ291" t="inlineStr">
@@ -54926,15 +54836,15 @@
       </c>
       <c r="AS291" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT291" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU291" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV291" t="inlineStr">
@@ -54969,7 +54879,7 @@
       </c>
       <c r="BB291" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC291" t="inlineStr">
@@ -55150,7 +55060,7 @@
       </c>
       <c r="AP292" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ292" t="inlineStr">
@@ -55160,15 +55070,15 @@
       </c>
       <c r="AS292" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT292" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU292" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV292" t="inlineStr">
@@ -55203,7 +55113,7 @@
       </c>
       <c r="BB292" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC292" t="inlineStr">
@@ -58804,11 +58714,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA311" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -58821,7 +58726,7 @@
       </c>
       <c r="AP311" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ311" t="inlineStr">
@@ -58831,15 +58736,15 @@
       </c>
       <c r="AS311" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT311" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU311" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV311" t="inlineStr">
@@ -59055,7 +58960,7 @@
       </c>
       <c r="AP312" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ312" t="inlineStr">
@@ -59065,15 +58970,15 @@
       </c>
       <c r="AS312" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT312" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU312" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV312" t="inlineStr">
@@ -61300,11 +61205,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA324" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -61317,7 +61217,7 @@
       </c>
       <c r="AP324" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ324" t="inlineStr">
@@ -61327,15 +61227,15 @@
       </c>
       <c r="AS324" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT324" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU324" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV324" t="inlineStr">
@@ -61370,7 +61270,7 @@
       </c>
       <c r="BB324" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC324" t="inlineStr">
@@ -61551,7 +61451,7 @@
       </c>
       <c r="AP325" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ325" t="inlineStr">
@@ -61561,15 +61461,15 @@
       </c>
       <c r="AS325" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT325" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU325" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV325" t="inlineStr">
@@ -61604,7 +61504,7 @@
       </c>
       <c r="BB325" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC325" t="inlineStr">
@@ -61693,11 +61593,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA326" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -61710,7 +61605,7 @@
       </c>
       <c r="AP326" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ326" t="inlineStr">
@@ -61720,15 +61615,15 @@
       </c>
       <c r="AS326" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT326" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU326" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV326" t="inlineStr">
@@ -61944,7 +61839,7 @@
       </c>
       <c r="AP327" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ327" t="inlineStr">
@@ -61954,15 +61849,15 @@
       </c>
       <c r="AS327" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU327" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV327" t="inlineStr">
@@ -65210,11 +65105,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA344" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -65227,7 +65117,7 @@
       </c>
       <c r="AP344" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ344" t="inlineStr">
@@ -65237,15 +65127,15 @@
       </c>
       <c r="AS344" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT344" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU344" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV344" t="inlineStr">
@@ -65461,7 +65351,7 @@
       </c>
       <c r="AP345" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ345" t="inlineStr">
@@ -65471,15 +65361,15 @@
       </c>
       <c r="AS345" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT345" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU345" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV345" t="inlineStr">
@@ -68875,11 +68765,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA363" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -68892,7 +68777,7 @@
       </c>
       <c r="AP363" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ363" t="inlineStr">
@@ -68902,15 +68787,15 @@
       </c>
       <c r="AS363" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT363" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU363" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV363" t="inlineStr">
@@ -68945,7 +68830,7 @@
       </c>
       <c r="BB363" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC363" t="inlineStr">
@@ -69126,7 +69011,7 @@
       </c>
       <c r="AP364" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ364" t="inlineStr">
@@ -69136,15 +69021,15 @@
       </c>
       <c r="AS364" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU364" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV364" t="inlineStr">
@@ -69179,7 +69064,7 @@
       </c>
       <c r="BB364" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC364" t="inlineStr">
@@ -69268,11 +69153,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA365" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -69285,7 +69165,7 @@
       </c>
       <c r="AP365" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ365" t="inlineStr">
@@ -69295,15 +69175,15 @@
       </c>
       <c r="AS365" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT365" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU365" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV365" t="inlineStr">
@@ -69519,7 +69399,7 @@
       </c>
       <c r="AP366" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ366" t="inlineStr">
@@ -69529,15 +69409,15 @@
       </c>
       <c r="AS366" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT366" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU366" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV366" t="inlineStr">
@@ -72785,11 +72665,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA383" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -72802,7 +72677,7 @@
       </c>
       <c r="AP383" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ383" t="inlineStr">
@@ -72812,15 +72687,15 @@
       </c>
       <c r="AS383" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT383" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU383" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV383" t="inlineStr">
@@ -73036,7 +72911,7 @@
       </c>
       <c r="AP384" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ384" t="inlineStr">
@@ -73046,15 +72921,15 @@
       </c>
       <c r="AS384" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT384" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU384" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV384" t="inlineStr">
@@ -75281,11 +75156,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA396" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -75298,7 +75168,7 @@
       </c>
       <c r="AP396" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ396" t="inlineStr">
@@ -75308,15 +75178,15 @@
       </c>
       <c r="AS396" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT396" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU396" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV396" t="inlineStr">
@@ -75351,7 +75221,7 @@
       </c>
       <c r="BB396" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC396" t="inlineStr">
@@ -75532,7 +75402,7 @@
       </c>
       <c r="AP397" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ397" t="inlineStr">
@@ -75542,15 +75412,15 @@
       </c>
       <c r="AS397" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT397" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU397" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV397" t="inlineStr">
@@ -75585,7 +75455,7 @@
       </c>
       <c r="BB397" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC397" t="inlineStr">
@@ -75674,11 +75544,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA398" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -75691,7 +75556,7 @@
       </c>
       <c r="AP398" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ398" t="inlineStr">
@@ -75701,15 +75566,15 @@
       </c>
       <c r="AS398" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT398" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU398" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV398" t="inlineStr">
@@ -75925,7 +75790,7 @@
       </c>
       <c r="AP399" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ399" t="inlineStr">
@@ -75935,15 +75800,15 @@
       </c>
       <c r="AS399" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT399" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU399" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV399" t="inlineStr">
@@ -79579,11 +79444,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA418" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -79596,7 +79456,7 @@
       </c>
       <c r="AP418" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ418" t="inlineStr">
@@ -79606,15 +79466,15 @@
       </c>
       <c r="AS418" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT418" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU418" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV418" t="inlineStr">
@@ -79830,7 +79690,7 @@
       </c>
       <c r="AP419" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ419" t="inlineStr">
@@ -79840,15 +79700,15 @@
       </c>
       <c r="AS419" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT419" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU419" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV419" t="inlineStr">
@@ -82075,11 +81935,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA431" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -82092,7 +81947,7 @@
       </c>
       <c r="AP431" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ431" t="inlineStr">
@@ -82102,15 +81957,15 @@
       </c>
       <c r="AS431" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT431" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU431" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV431" t="inlineStr">
@@ -82145,7 +82000,7 @@
       </c>
       <c r="BB431" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC431" t="inlineStr">
@@ -82326,7 +82181,7 @@
       </c>
       <c r="AP432" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ432" t="inlineStr">
@@ -82336,15 +82191,15 @@
       </c>
       <c r="AS432" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT432" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU432" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV432" t="inlineStr">
@@ -82379,7 +82234,7 @@
       </c>
       <c r="BB432" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC432" t="inlineStr">
@@ -82468,11 +82323,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA433" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -82485,7 +82335,7 @@
       </c>
       <c r="AP433" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ433" t="inlineStr">
@@ -82495,15 +82345,15 @@
       </c>
       <c r="AS433" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT433" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU433" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV433" t="inlineStr">
@@ -82719,7 +82569,7 @@
       </c>
       <c r="AP434" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ434" t="inlineStr">
@@ -82729,15 +82579,15 @@
       </c>
       <c r="AS434" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT434" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU434" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV434" t="inlineStr">
@@ -85985,11 +85835,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U451" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA451" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -86002,7 +85847,7 @@
       </c>
       <c r="AP451" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ451" t="inlineStr">
@@ -86012,15 +85857,15 @@
       </c>
       <c r="AS451" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT451" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU451" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV451" t="inlineStr">
@@ -86236,7 +86081,7 @@
       </c>
       <c r="AP452" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ452" t="inlineStr">
@@ -86246,15 +86091,15 @@
       </c>
       <c r="AS452" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU452" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV452" t="inlineStr">

--- a/diseases/d043/2000-2004.xlsx
+++ b/diseases/d043/2000-2004.xlsx
@@ -9286,11 +9286,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9303,7 +9298,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
@@ -9313,15 +9308,15 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -9537,7 +9532,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
@@ -9547,15 +9542,15 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -15294,11 +15289,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15311,7 +15301,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
@@ -15321,15 +15311,15 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -15545,7 +15535,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
@@ -15555,15 +15545,15 @@
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -28857,11 +28847,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28874,7 +28859,7 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
@@ -28884,15 +28869,15 @@
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
@@ -29108,7 +29093,7 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ158" t="inlineStr">
@@ -29118,15 +29103,15 @@
       </c>
       <c r="AS158" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
@@ -36417,11 +36402,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36434,7 +36414,7 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ196" t="inlineStr">
@@ -36444,15 +36424,15 @@
       </c>
       <c r="AS196" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
@@ -36668,7 +36648,7 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ197" t="inlineStr">
@@ -36678,15 +36658,15 @@
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
@@ -42420,11 +42400,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42437,7 +42412,7 @@
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ227" t="inlineStr">
@@ -42447,15 +42422,15 @@
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
@@ -42671,7 +42646,7 @@
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
@@ -42681,15 +42656,15 @@
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
@@ -49199,11 +49174,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49216,7 +49186,7 @@
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ262" t="inlineStr">
@@ -49226,15 +49196,15 @@
       </c>
       <c r="AS262" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
@@ -49450,7 +49420,7 @@
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ263" t="inlineStr">
@@ -49460,15 +49430,15 @@
       </c>
       <c r="AS263" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
@@ -55983,11 +55953,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA297" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -56000,7 +55965,7 @@
       </c>
       <c r="AP297" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ297" t="inlineStr">
@@ -56010,15 +55975,15 @@
       </c>
       <c r="AS297" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU297" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV297" t="inlineStr">
@@ -56234,7 +56199,7 @@
       </c>
       <c r="AP298" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ298" t="inlineStr">
@@ -56244,15 +56209,15 @@
       </c>
       <c r="AS298" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT298" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV298" t="inlineStr">
@@ -62762,11 +62727,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA332" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -62779,7 +62739,7 @@
       </c>
       <c r="AP332" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ332" t="inlineStr">
@@ -62789,15 +62749,15 @@
       </c>
       <c r="AS332" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU332" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV332" t="inlineStr">
@@ -63013,7 +62973,7 @@
       </c>
       <c r="AP333" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ333" t="inlineStr">
@@ -63023,15 +62983,15 @@
       </c>
       <c r="AS333" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU333" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV333" t="inlineStr">
@@ -69934,11 +69894,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U369" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA369" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -69951,7 +69906,7 @@
       </c>
       <c r="AP369" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ369" t="inlineStr">
@@ -69961,15 +69916,15 @@
       </c>
       <c r="AS369" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT369" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU369" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV369" t="inlineStr">
@@ -70185,7 +70140,7 @@
       </c>
       <c r="AP370" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ370" t="inlineStr">
@@ -70195,15 +70150,15 @@
       </c>
       <c r="AS370" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT370" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU370" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV370" t="inlineStr">
@@ -76713,11 +76668,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U404" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA404" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -76730,7 +76680,7 @@
       </c>
       <c r="AP404" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ404" t="inlineStr">
@@ -76740,15 +76690,15 @@
       </c>
       <c r="AS404" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT404" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU404" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV404" t="inlineStr">
@@ -76964,7 +76914,7 @@
       </c>
       <c r="AP405" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ405" t="inlineStr">
@@ -76974,15 +76924,15 @@
       </c>
       <c r="AS405" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT405" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU405" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV405" t="inlineStr">
@@ -83492,11 +83442,6 @@
           <t>nbs_computed</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
-        </is>
-      </c>
       <c r="AA439" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -83509,7 +83454,7 @@
       </c>
       <c r="AP439" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ439" t="inlineStr">
@@ -83519,15 +83464,15 @@
       </c>
       <c r="AS439" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT439" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU439" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV439" t="inlineStr">
@@ -83743,7 +83688,7 @@
       </c>
       <c r="AP440" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ440" t="inlineStr">
@@ -83753,15 +83698,15 @@
       </c>
       <c r="AS440" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TYPHUS</t>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
         </is>
       </c>
       <c r="AT440" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU440" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV440" t="inlineStr">

--- a/diseases/d043/2000-2004.xlsx
+++ b/diseases/d043/2000-2004.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,13 +788,23 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -909,6 +924,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -921,13 +941,23 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1047,6 +1077,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1059,13 +1094,23 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1185,6 +1230,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1197,13 +1247,23 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1323,6 +1383,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1335,13 +1400,23 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1461,6 +1536,11 @@
       <c r="R7" t="n">
         <v>0.01491499052003203</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1473,13 +1553,23 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1599,6 +1689,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1611,13 +1706,23 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1737,6 +1842,11 @@
       <c r="R9" t="n">
         <v>0.01491499052003203</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1749,13 +1859,23 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1875,6 +1995,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1887,13 +2012,23 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2013,6 +2148,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2025,13 +2165,23 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2151,6 +2301,11 @@
       <c r="R12" t="n">
         <v>0.02982998104006405</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2163,13 +2318,23 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2289,6 +2454,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2301,13 +2471,23 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2427,6 +2607,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2439,13 +2624,23 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2565,6 +2760,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2577,13 +2777,23 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2703,6 +2913,11 @@
       <c r="R16" t="n">
         <v>0.01476180680677245</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2715,13 +2930,23 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2841,6 +3066,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2853,13 +3083,23 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2979,6 +3219,11 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2991,13 +3236,23 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3117,6 +3372,11 @@
       <c r="R19" t="n">
         <v>0.01476180680677245</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3129,13 +3389,23 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3255,6 +3525,11 @@
       <c r="R20" t="n">
         <v>0.0295236136135449</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3267,13 +3542,23 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3393,6 +3678,11 @@
       <c r="R21" t="n">
         <v>0.01476180680677245</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3405,13 +3695,23 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3531,6 +3831,11 @@
       <c r="R22" t="n">
         <v>0.01476180680677245</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3543,13 +3848,23 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3669,6 +3984,11 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3681,13 +4001,23 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3807,6 +4137,11 @@
       <c r="R24" t="n">
         <v>0.01476180680677245</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3819,13 +4154,23 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3945,6 +4290,11 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3957,13 +4307,23 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -4083,6 +4443,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4095,13 +4460,23 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -4221,6 +4596,11 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4233,13 +4613,23 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -4359,6 +4749,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4371,13 +4766,23 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -4497,6 +4902,11 @@
       <c r="R29" t="n">
         <v>0.01465972899878376</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4509,13 +4919,23 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -4635,6 +5055,11 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4647,13 +5072,23 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -4773,6 +5208,11 @@
       <c r="R31" t="n">
         <v>0.02931945799756751</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4785,13 +5225,23 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -4911,6 +5361,11 @@
       <c r="R32" t="n">
         <v>0.01465972899878376</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4923,13 +5378,23 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -5049,6 +5514,11 @@
       <c r="R33" t="n">
         <v>0.02931945799756751</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5061,13 +5531,23 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -5187,6 +5667,11 @@
       <c r="R34" t="n">
         <v>0.05863891599513502</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5199,13 +5684,23 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -5325,6 +5820,11 @@
       <c r="R35" t="n">
         <v>0.01465972899878376</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5337,13 +5837,23 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -5463,6 +5973,11 @@
       <c r="R36" t="n">
         <v>0.02931945799756751</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5475,13 +5990,23 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -5601,6 +6126,11 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5613,13 +6143,23 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -5739,6 +6279,11 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5751,13 +6296,23 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -5877,6 +6432,11 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5889,13 +6449,23 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -6015,6 +6585,11 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6027,13 +6602,23 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -6153,6 +6738,11 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6165,13 +6755,23 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV41" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -6291,6 +6891,11 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6303,13 +6908,23 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -6429,6 +7044,11 @@
       <c r="R43" t="n">
         <v>0.01457958349483259</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6441,13 +7061,23 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -6567,6 +7197,11 @@
       <c r="R44" t="n">
         <v>0.01457958349483259</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6579,13 +7214,23 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV44" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -6705,6 +7350,11 @@
       <c r="R45" t="n">
         <v>0.01457958349483259</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6717,13 +7367,23 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -6843,6 +7503,11 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6855,13 +7520,23 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -6981,6 +7656,11 @@
       <c r="R47" t="n">
         <v>0.05831833397933037</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6993,13 +7673,23 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
       </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV47" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -7119,6 +7809,11 @@
       <c r="R48" t="n">
         <v>0.07289791747416298</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7131,13 +7826,23 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -7257,6 +7962,11 @@
       <c r="R49" t="n">
         <v>0.02915916698966519</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7269,13 +7979,23 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
       </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV49" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -9123,6 +9843,11 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9135,13 +9860,23 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
       </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV62" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -11709,6 +12444,11 @@
       <c r="R80" t="n">
         <v>0</v>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11721,13 +12461,23 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
       </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV80" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -14007,6 +14757,11 @@
       <c r="R96" t="n">
         <v>0.01451765771820021</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14019,13 +14774,23 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
       </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV96" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -17025,6 +17790,11 @@
       <c r="R117" t="n">
         <v>0</v>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17037,13 +17807,23 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
       </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV117" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -19611,6 +20391,11 @@
       <c r="R135" t="n">
         <v>0</v>
       </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19623,13 +20408,23 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
       </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV135" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -21909,6 +22704,11 @@
       <c r="R151" t="n">
         <v>0.05807063087280085</v>
       </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21921,13 +22721,23 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
       </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV151" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -24495,6 +25305,11 @@
       <c r="R169" t="n">
         <v>0.04355297315460064</v>
       </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24507,13 +25322,23 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
       </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV169" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -27081,6 +27906,11 @@
       <c r="R187" t="n">
         <v>0.02903531543640043</v>
       </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27093,13 +27923,23 @@
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
         <v>0</v>
       </c>
+      <c r="AU187" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV187" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -29667,6 +30507,11 @@
       <c r="R205" t="n">
         <v>0.01451765771820021</v>
       </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29679,13 +30524,23 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
         <v>0</v>
       </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV205" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -32397,6 +33252,11 @@
       <c r="R224" t="n">
         <v>0.01451765771820021</v>
       </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32409,13 +33269,23 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr"/>
       <c r="AT224" t="n">
         <v>0</v>
       </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV224" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -34983,6 +35853,11 @@
       <c r="R242" t="n">
         <v>0.04355297315460064</v>
       </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34995,13 +35870,23 @@
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR242" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS242" t="inlineStr"/>
       <c r="AT242" t="n">
         <v>0</v>
       </c>
+      <c r="AU242" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV242" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -37425,6 +38310,11 @@
       <c r="R259" t="n">
         <v>0.04355297315460064</v>
       </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA259" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37437,12 +38327,22 @@
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS259" t="inlineStr"/>
       <c r="AT259" t="n">
         <v>0</v>
+      </c>
+      <c r="AU259" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
